--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2024/IDAHO_2024.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2024/IDAHO_2024.xlsx
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C174">
@@ -12426,7 +12426,7 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>Ziltlaltepec De Trinidad Sanchez Santos</t>
+          <t>Zitlaltepec De Trinidad Sanchez Santos</t>
         </is>
       </c>
       <c r="C671">
